--- a/AAII_Financials/Yearly/HPK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPK_YR_FIN.xlsx
@@ -2309,7 +2309,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2933400</v>
+        <v>2934400</v>
       </c>
       <c r="E48" s="3">
         <v>2850300</v>
@@ -2489,7 +2489,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20400</v>
+        <v>19400</v>
       </c>
       <c r="E52" s="3">
         <v>17900</v>
